--- a/output/xlsx/data_tp2.xlsx
+++ b/output/xlsx/data_tp2.xlsx
@@ -461,7 +461,7 @@
         <v>5</v>
       </c>
       <c r="L2">
-        <v>0.7476</v>
+        <v>74.76000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -509,7 +509,7 @@
         <v>12</v>
       </c>
       <c r="L3">
-        <v>0.607</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="4">
@@ -557,7 +557,7 @@
         <v>6</v>
       </c>
       <c r="L4">
-        <v>0.6</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -605,7 +605,7 @@
         <v>2</v>
       </c>
       <c r="L5">
-        <v>0.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -653,7 +653,7 @@
         <v>6</v>
       </c>
       <c r="L6">
-        <v>0.5133</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="7">
@@ -701,7 +701,7 @@
         <v>2</v>
       </c>
       <c r="L7">
-        <v>0.5375</v>
+        <v>53.75</v>
       </c>
     </row>
     <row r="8">
@@ -749,7 +749,7 @@
         <v>2</v>
       </c>
       <c r="L8">
-        <v>0.2082</v>
+        <v>20.82</v>
       </c>
     </row>
     <row r="9">
@@ -797,7 +797,7 @@
         <v>2</v>
       </c>
       <c r="L9">
-        <v>0.226</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="10">
@@ -845,7 +845,7 @@
         <v>3</v>
       </c>
       <c r="L10">
-        <v>0.4175</v>
+        <v>41.75</v>
       </c>
     </row>
     <row r="11">
@@ -893,7 +893,7 @@
         <v>5</v>
       </c>
       <c r="L11">
-        <v>0.4417</v>
+        <v>44.17</v>
       </c>
     </row>
     <row r="12">
@@ -941,7 +941,7 @@
         <v>2</v>
       </c>
       <c r="L12">
-        <v>0.378</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="13">
@@ -989,7 +989,7 @@
         <v>3</v>
       </c>
       <c r="L13">
-        <v>0.4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -1037,7 +1037,7 @@
         <v>3</v>
       </c>
       <c r="L14">
-        <v>0.475</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="15">
@@ -1085,7 +1085,7 @@
         <v>3</v>
       </c>
       <c r="L15">
-        <v>0.5660000000000001</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="16">
@@ -1133,7 +1133,7 @@
         <v>4</v>
       </c>
       <c r="L16">
-        <v>0.225</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="17">
@@ -1181,7 +1181,7 @@
         <v>3</v>
       </c>
       <c r="L17">
-        <v>0.3225</v>
+        <v>32.25</v>
       </c>
     </row>
   </sheetData>
